--- a/data/entrada/docencia/doctorados actividad centro.xlsx
+++ b/data/entrada/docencia/doctorados actividad centro.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amarzal/_Activo/eco/CoAna/data/entrada/docencia/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D755F68-7C09-4E41-8315-048DD03E8232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="34320" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
   <si>
     <t>estudio</t>
   </si>
@@ -101,16 +107,85 @@
   </si>
   <si>
     <t>Programa de doctorat en Química Teòrica i Modelització Computacional per la Universidad Autónoma de Madrid; la Universidad Complutense de Madrid; la Universidad de Barcelona; la Universidad de Cantabria; la Universidad de Extremadura; la Universidad de les Illes Balears; la Universidad de Murcia; la Universidad de Oviedo; la Universidad de Sevilla; la Universidad de Vigo; la Universidad del País Vasco/Euskal Herriko Unibertsitatea; la Universitat Jaume I de Castelló i la Universitat de València (Estudi General)</t>
+  </si>
+  <si>
+    <t>doc-c</t>
+  </si>
+  <si>
+    <t>doc-cbs</t>
+  </si>
+  <si>
+    <t>doc-lal</t>
+  </si>
+  <si>
+    <t>doc-ce</t>
+  </si>
+  <si>
+    <t>doc-titm</t>
+  </si>
+  <si>
+    <t>doc-educación</t>
+  </si>
+  <si>
+    <t>doc-psi</t>
+  </si>
+  <si>
+    <t>doc-ee</t>
+  </si>
+  <si>
+    <t>doc-informática</t>
+  </si>
+  <si>
+    <t>doc-eipcd</t>
+  </si>
+  <si>
+    <t>doc-d</t>
+  </si>
+  <si>
+    <t>doc-cc</t>
+  </si>
+  <si>
+    <t>doc-hec</t>
+  </si>
+  <si>
+    <t>doc-eig</t>
+  </si>
+  <si>
+    <t>doc-qs</t>
+  </si>
+  <si>
+    <t>doc-dlci</t>
+  </si>
+  <si>
+    <t>doc-dgpeb</t>
+  </si>
+  <si>
+    <t>doc-hpt</t>
+  </si>
+  <si>
+    <t>doc-ha</t>
+  </si>
+  <si>
+    <t>doc-marqueting</t>
+  </si>
+  <si>
+    <t>doc-ed</t>
+  </si>
+  <si>
+    <t>doc-qtc</t>
+  </si>
+  <si>
+    <t>ed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,36 +226,52 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
+      <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
     </dxf>
-    <dxf/>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;[Red]\-#,##0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:G23" totalsRowShown="0">
-  <autoFilter ref="A1:G23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Frame0" displayName="Frame0" ref="A1:G23" totalsRowShown="0">
+  <autoFilter ref="A1:G23" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="estudio" dataDxfId="0"/>
-    <tableColumn id="2" name="nombre_doctorado" dataDxfId="1"/>
-    <tableColumn id="3" name="n_doctorados_planes" dataDxfId="0"/>
-    <tableColumn id="4" name="n_tesis_activas_2025" dataDxfId="0"/>
-    <tableColumn id="5" name="n_alumnos_unicos" dataDxfId="0"/>
-    <tableColumn id="6" name="actividad" dataDxfId="1"/>
-    <tableColumn id="7" name="centro" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="estudio" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="nombre_doctorado"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="n_doctorados_planes" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="n_tesis_activas_2025" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="n_alumnos_unicos" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="actividad"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="centro"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -218,7 +309,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -252,6 +343,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -286,9 +378,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -461,11 +554,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="65.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>90162</v>
       </c>
@@ -504,10 +601,14 @@
       <c r="E2" s="1">
         <v>137</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="F2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>90163</v>
       </c>
@@ -523,10 +624,14 @@
       <c r="E3" s="1">
         <v>110</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>90177</v>
       </c>
@@ -542,10 +647,14 @@
       <c r="E4" s="1">
         <v>86</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>90165</v>
       </c>
@@ -561,10 +670,14 @@
       <c r="E5" s="1">
         <v>80</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="F5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>90183</v>
       </c>
@@ -580,10 +693,14 @@
       <c r="E6" s="1">
         <v>78</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="F6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>90170</v>
       </c>
@@ -599,10 +716,14 @@
       <c r="E7" s="1">
         <v>71</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>90180</v>
       </c>
@@ -618,10 +739,14 @@
       <c r="E8" s="1">
         <v>69</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>90169</v>
       </c>
@@ -637,10 +762,14 @@
       <c r="E9" s="1">
         <v>67</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="F9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>90176</v>
       </c>
@@ -656,10 +785,14 @@
       <c r="E10" s="1">
         <v>62</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>90172</v>
       </c>
@@ -675,10 +808,14 @@
       <c r="E11" s="1">
         <v>55</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="F11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>90168</v>
       </c>
@@ -694,10 +831,14 @@
       <c r="E12" s="1">
         <v>55</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="F12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>90164</v>
       </c>
@@ -713,10 +854,14 @@
       <c r="E13" s="1">
         <v>55</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>90175</v>
       </c>
@@ -732,10 +877,14 @@
       <c r="E14" s="1">
         <v>26</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>90171</v>
       </c>
@@ -751,10 +900,14 @@
       <c r="E15" s="1">
         <v>24</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="F15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>90181</v>
       </c>
@@ -770,10 +923,14 @@
       <c r="E16" s="1">
         <v>22</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="F16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>90166</v>
       </c>
@@ -789,10 +946,14 @@
       <c r="E17" s="1">
         <v>21</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>90167</v>
       </c>
@@ -808,10 +969,14 @@
       <c r="E18" s="1">
         <v>18</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="F18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>90197</v>
       </c>
@@ -827,10 +992,14 @@
       <c r="E19" s="1">
         <v>16</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>90174</v>
       </c>
@@ -846,10 +1015,14 @@
       <c r="E20" s="1">
         <v>15</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="F20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>90178</v>
       </c>
@@ -865,10 +1038,14 @@
       <c r="E21" s="1">
         <v>15</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="F21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>90173</v>
       </c>
@@ -884,10 +1061,14 @@
       <c r="E22" s="1">
         <v>10</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="F22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>90182</v>
       </c>
@@ -903,8 +1084,12 @@
       <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="F23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
